--- a/data/用户/软件23选88学生名单.xlsx
+++ b/data/用户/软件23选88学生名单.xlsx
@@ -1059,7 +1059,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
